--- a/Data/True_data/current_data/footnotes/ppe_sched.xlsx
+++ b/Data/True_data/current_data/footnotes/ppe_sched.xlsx
@@ -471,7 +471,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
@@ -491,7 +490,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>593.5700000000001</v>
+        <v>430.58</v>
       </c>
     </row>
     <row r="7">
@@ -501,7 +500,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>80.54000000000001</v>
+        <v>65.93000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +510,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="9">
@@ -521,7 +520,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>-58.45</v>
+        <v>-40.4</v>
       </c>
     </row>
     <row r="10">
@@ -531,7 +530,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>-224.68</v>
+        <v>-150.8</v>
       </c>
     </row>
     <row r="11">
@@ -541,7 +540,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>368.89</v>
+        <v>279.78</v>
       </c>
     </row>
   </sheetData>
